--- a/dati/CONSEGNE/CONSEGNE_26-03-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_26-03-2026/punti_consegna.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Punti consegna" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,8 @@
           <t>p10839_p00000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D2" t="n">
+        <v>3205</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -532,10 +530,8 @@
           <t>p11560_p00000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D3" t="n">
+        <v>3110</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -580,10 +576,8 @@
           <t>p12264_p00000</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D4" t="n">
+        <v>3209</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -628,10 +622,8 @@
           <t>p12400_p00000</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D5" t="n">
+        <v>3206</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -676,10 +668,8 @@
           <t>p12472_p1855</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D6" t="n">
+        <v>3206</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -724,10 +714,8 @@
           <t>p12528_p00000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D7" t="n">
+        <v>3209</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -772,10 +760,8 @@
           <t>p13231_p00000</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D8" t="n">
+        <v>3206</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -820,10 +806,8 @@
           <t>p13495_p00000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D9" t="n">
+        <v>3206</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -868,10 +852,8 @@
           <t>p13590_p00000</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3206</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -916,10 +898,8 @@
           <t>p13927_p1853</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D11" t="n">
+        <v>3206</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -964,10 +944,8 @@
           <t>p13947_p00000</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D12" t="n">
+        <v>3205</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1012,10 +990,8 @@
           <t>p14010_p00000</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D13" t="n">
+        <v>3110</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1060,10 +1036,8 @@
           <t>p14089_p2654</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D14" t="n">
+        <v>3209</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1108,10 +1082,8 @@
           <t>p2040_p00000</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D15" t="n">
+        <v>3111</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1156,10 +1128,8 @@
           <t>p2041_p00000</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D16" t="n">
+        <v>3111</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1204,10 +1174,8 @@
           <t>p2042_p00000</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D17" t="n">
+        <v>3111</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1252,10 +1220,8 @@
           <t>p2043_p00000</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D18" t="n">
+        <v>3111</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1300,10 +1266,8 @@
           <t>p2067_p00000</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D19" t="n">
+        <v>3110</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1348,10 +1312,8 @@
           <t>p2068_p00000</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D20" t="n">
+        <v>3110</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1396,10 +1358,8 @@
           <t>p2099_p00000</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D21" t="n">
+        <v>3206</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1444,10 +1404,8 @@
           <t>p2109_p1750</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D22" t="n">
+        <v>3110</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1492,10 +1450,8 @@
           <t>p2114_p1733</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D23" t="n">
+        <v>3209</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1496,8 @@
           <t>p2158_p00000</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D24" t="n">
+        <v>3110</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1588,10 +1542,8 @@
           <t>p2160_p00000</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D25" t="n">
+        <v>3110</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1636,10 +1588,8 @@
           <t>p2180_p1964</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D26" t="n">
+        <v>3209</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1684,10 +1634,8 @@
           <t>p2181_p1965</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D27" t="n">
+        <v>3209</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1710,10 +1658,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>45.5921909</v>
+        <v>45.6511298</v>
       </c>
       <c r="J27" t="n">
-        <v>12.5044174</v>
+        <v>12.6057277</v>
       </c>
     </row>
     <row r="28">
@@ -1732,10 +1680,8 @@
           <t>p2182_p1963</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D28" t="n">
+        <v>3209</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1780,10 +1726,8 @@
           <t>p2192_p2008</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D29" t="n">
+        <v>3111</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1828,10 +1772,8 @@
           <t>p2193_p2007</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D30" t="n">
+        <v>3111</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1876,10 +1818,8 @@
           <t>p2208_p00000</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D31" t="n">
+        <v>3111</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1924,10 +1864,8 @@
           <t>p2209_p1930</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D32" t="n">
+        <v>3111</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1972,10 +1910,8 @@
           <t>p2210_p00000</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D33" t="n">
+        <v>3111</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2020,10 +1956,8 @@
           <t>p2211_p00000</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D34" t="n">
+        <v>3111</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2068,10 +2002,8 @@
           <t>p2240_p1811</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D35" t="n">
+        <v>3111</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2116,10 +2048,8 @@
           <t>p2242_p1809</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D36" t="n">
+        <v>3111</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2156,18 +2086,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>p00000</t>
+          <t>p1807</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>p2243_p00000</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+          <t>p2243_p1807</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3111</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2212,10 +2140,8 @@
           <t>p2244_p1810</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D38" t="n">
+        <v>3111</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2260,10 +2186,8 @@
           <t>p2247_p1707</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D39" t="n">
+        <v>3111</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2308,10 +2232,8 @@
           <t>p2248_p1705</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D40" t="n">
+        <v>3111</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2356,10 +2278,8 @@
           <t>p2249_p1699</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D41" t="n">
+        <v>3111</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2404,10 +2324,8 @@
           <t>p2254_p1861</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D42" t="n">
+        <v>3206</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2452,10 +2370,8 @@
           <t>p2267_p1929</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D43" t="n">
+        <v>3206</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2500,10 +2416,8 @@
           <t>p2301_p1950</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D44" t="n">
+        <v>3205</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2548,10 +2462,8 @@
           <t>p2302_p1951</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D45" t="n">
+        <v>3205</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2596,10 +2508,8 @@
           <t>p2318_p2012</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D46" t="n">
+        <v>3209</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2644,10 +2554,8 @@
           <t>p2319_p2013</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D47" t="n">
+        <v>3209</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2684,22 +2592,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>p00000</t>
+          <t>p1848</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>p2325_p00000</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+          <t>p2325_p1848</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3110</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>"DUCA DEGLI ABRUZZI"</t>
+          <t>S. CATERINA D'ESTE - DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2740,10 +2646,8 @@
           <t>p2326_p1847</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D49" t="n">
+        <v>3110</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2788,10 +2692,8 @@
           <t>p2327_p1849</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D50" t="n">
+        <v>3110</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2836,10 +2738,8 @@
           <t>p2328_p1851</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D51" t="n">
+        <v>3110</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2884,10 +2784,8 @@
           <t>p2339_p00000</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D52" t="n">
+        <v>3209</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2932,10 +2830,8 @@
           <t>p2340_p1789</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D53" t="n">
+        <v>3209</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2980,10 +2876,8 @@
           <t>p2353_p00000</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D54" t="n">
+        <v>3206</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3028,10 +2922,8 @@
           <t>p2354_p1793</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D55" t="n">
+        <v>3206</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3076,10 +2968,8 @@
           <t>p2355_p1792</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D56" t="n">
+        <v>3205</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3124,10 +3014,8 @@
           <t>p2356_p1794</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D57" t="n">
+        <v>3205</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3172,10 +3060,8 @@
           <t>p2357_p1704</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D58" t="n">
+        <v>3205</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3220,10 +3106,8 @@
           <t>p2359_p1874</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D59" t="n">
+        <v>3209</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3246,10 +3130,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>45.7778637</v>
+        <v>45.78058984536306</v>
       </c>
       <c r="J59" t="n">
-        <v>12.8411426</v>
+        <v>12.84476537118256</v>
       </c>
     </row>
     <row r="60">
@@ -3268,10 +3152,8 @@
           <t>p2360_p1865</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D60" t="n">
+        <v>3209</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3294,10 +3176,10 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>45.7838418</v>
+        <v>45.78399892049632</v>
       </c>
       <c r="J60" t="n">
-        <v>12.8289614</v>
+        <v>12.82970884230005</v>
       </c>
     </row>
     <row r="61">
@@ -3316,10 +3198,8 @@
           <t>p2361_p1863</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D61" t="n">
+        <v>3209</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3342,10 +3222,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>45.771588</v>
+        <v>45.6511298</v>
       </c>
       <c r="J61" t="n">
-        <v>12.8330972</v>
+        <v>12.6057277</v>
       </c>
     </row>
     <row r="62">
@@ -3364,10 +3244,8 @@
           <t>p2362_p1866</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D62" t="n">
+        <v>3209</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3390,10 +3268,10 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>45.778982</v>
+        <v>45.77787456540089</v>
       </c>
       <c r="J62" t="n">
-        <v>12.7997797</v>
+        <v>12.79991559848095</v>
       </c>
     </row>
     <row r="63">
@@ -3412,10 +3290,8 @@
           <t>p2363_p1867</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D63" t="n">
+        <v>3209</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3438,10 +3314,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>45.7785716</v>
+        <v>45.78346752983553</v>
       </c>
       <c r="J63" t="n">
-        <v>12.7905998</v>
+        <v>12.76019427991685</v>
       </c>
     </row>
     <row r="64">
@@ -3460,10 +3336,8 @@
           <t>p2364_p1800</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D64" t="n">
+        <v>3110</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3508,10 +3382,8 @@
           <t>p2365_p00000</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D65" t="n">
+        <v>3110</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3556,10 +3428,8 @@
           <t>p2396_p00000</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D66" t="n">
+        <v>3206</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3604,10 +3474,8 @@
           <t>p2397_p00000</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D67" t="n">
+        <v>3206</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3652,10 +3520,8 @@
           <t>p2403_p00000</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D68" t="n">
+        <v>3111</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3700,10 +3566,8 @@
           <t>p2404_p00000</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D69" t="n">
+        <v>3111</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3748,10 +3612,8 @@
           <t>p2415_p2645</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D70" t="n">
+        <v>3111</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3796,10 +3658,8 @@
           <t>p2416_p2647</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
+      <c r="D71" t="n">
+        <v>3111</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3844,10 +3704,8 @@
           <t>p2427_p00000</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D72" t="n">
+        <v>3110</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3892,10 +3750,8 @@
           <t>p2428_p00000</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D73" t="n">
+        <v>3110</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3940,10 +3796,8 @@
           <t>p2429_p1956</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D74" t="n">
+        <v>3110</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3988,10 +3842,8 @@
           <t>p2430_p1957</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D75" t="n">
+        <v>3110</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4036,10 +3888,8 @@
           <t>p6337_p1971</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D76" t="n">
+        <v>3110</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4084,10 +3934,8 @@
           <t>p6419_p1743</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D77" t="n">
+        <v>3110</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4132,10 +3980,8 @@
           <t>p6524_p00000</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D78" t="n">
+        <v>3206</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4180,10 +4026,8 @@
           <t>p6525_p00000</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D79" t="n">
+        <v>3206</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4228,10 +4072,8 @@
           <t>p6526_p00000</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D80" t="n">
+        <v>3206</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4276,10 +4118,8 @@
           <t>p6527_p00000</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D81" t="n">
+        <v>3205</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4324,10 +4164,8 @@
           <t>p6528_p00000</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D82" t="n">
+        <v>3206</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4372,10 +4210,8 @@
           <t>p7719_p00000</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D83" t="n">
+        <v>3205</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4420,10 +4256,8 @@
           <t>p8650_p1742</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D84" t="n">
+        <v>3110</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4468,10 +4302,8 @@
           <t>p8652_p1856</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D85" t="n">
+        <v>3206</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4516,10 +4348,8 @@
           <t>p8678_p1858</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D86" t="n">
+        <v>3206</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4564,10 +4394,8 @@
           <t>p8767_p00000</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D87" t="n">
+        <v>3205</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4612,10 +4440,8 @@
           <t>p8831_p00000</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
+      <c r="D88" t="n">
+        <v>3205</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4660,10 +4486,8 @@
           <t>p8847_p00000</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3206</t>
-        </is>
+      <c r="D89" t="n">
+        <v>3206</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4708,10 +4532,8 @@
           <t>p8992_p2023</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3110</t>
-        </is>
+      <c r="D90" t="n">
+        <v>3110</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4756,10 +4578,8 @@
           <t>p9148_p00000</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
+      <c r="D91" t="n">
+        <v>3209</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4782,10 +4602,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>45.6512142</v>
+        <v>45.6511298</v>
       </c>
       <c r="J91" t="n">
-        <v>12.6033814</v>
+        <v>12.6057277</v>
       </c>
     </row>
     <row r="92">
@@ -4804,10 +4624,8 @@
           <t>p00000_p1706</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="D92" t="n">
+        <v>4111</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4829,8 +4647,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>45.6450621</v>
+      </c>
+      <c r="J92" t="n">
+        <v>11.7840418</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4848,10 +4670,8 @@
           <t>p00000_p1708</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="D93" t="n">
+        <v>4111</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4873,8 +4693,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>45.6450621</v>
+      </c>
+      <c r="J93" t="n">
+        <v>11.7840418</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4892,10 +4716,8 @@
           <t>p00000_p1791</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
+      <c r="D94" t="n">
+        <v>4119</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4940,10 +4762,8 @@
           <t>p00000_p1795</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
+      <c r="D95" t="n">
+        <v>4119</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4965,8 +4785,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>45.6584726</v>
+      </c>
+      <c r="J95" t="n">
+        <v>13.0252235</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4984,10 +4808,8 @@
           <t>p00000_p1797</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="D96" t="n">
+        <v>4111</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5009,8 +4831,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>45.5391746</v>
+      </c>
+      <c r="J96" t="n">
+        <v>11.7896669</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5020,27 +4846,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>p1807</t>
+          <t>p1819</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>p00000_p1807</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+          <t>p00000_p1819</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>4111</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Campo S.Martino-Marsango</t>
+          <t>G Rodari - Loreggiola</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Via Alcide De Gasperi 43, 35010 Campo San Martino (PD)</t>
+          <t>Via Pio X N. 13, 35010 Loreggia (PD)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5053,8 +4877,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>45.6100998</v>
+      </c>
+      <c r="J97" t="n">
+        <v>11.9182903</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5064,27 +4892,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>p1819</t>
+          <t>p1901</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>p00000_p1819</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+          <t>p00000_p1901</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4111</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>G Rodari - Loreggiola</t>
+          <t>VITTORINO DA FELTRE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Via Pio X N. 13, 35010 Loreggia (PD)</t>
+          <t>VIA G.B.ROSSI 25, 30033 NOALE (VENEZIA)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5098,10 +4924,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>45.6100998</v>
+        <v>45.5511278606687</v>
       </c>
       <c r="J98" t="n">
-        <v>11.9182903</v>
+        <v>12.066637949173</v>
       </c>
     </row>
     <row r="99">
@@ -5112,32 +4938,30 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>p1848</t>
+          <t>p1911</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>p00000_p1848</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
+          <t>p00000_p1911</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>4110</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>S. Caterina D'Este -Duca Degli Abruzzi</t>
+          <t>Castelbaldo-Rosa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Via Roma 32, 35049 S. Caterina D'Este (PD)</t>
+          <t>Piazza Della Resistenza 1B, 35040 Castelbaldo (PD)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5145,8 +4969,12 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>45.1204921360993</v>
+      </c>
+      <c r="J99" t="n">
+        <v>11.4518790989041</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5156,32 +4984,30 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>p1901</t>
+          <t>p2011</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>p00000_p1901</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+          <t>p00000_p2011</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>4110</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>VITTORINO DA FELTRE</t>
+          <t>Casale Di Scodosia-Marconi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VIA G.B.ROSSI 25, 30033 NOALE (VENEZIA)</t>
+          <t>Piazza Matteotti 32/33, 35040 Casale Di Scodosia (PD)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5190,105 +5016,9 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>45.5511278606687</v>
+        <v>45.1883645404963</v>
       </c>
       <c r="J100" t="n">
-        <v>12.066637949173</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>p00000</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>p1911</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>p00000_p1911</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Castelbaldo-Rosa</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Piazza Della Resistenza 1B, 35040 Castelbaldo (PD)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>45.1204921360993</v>
-      </c>
-      <c r="J101" t="n">
-        <v>11.4518790989041</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>p00000</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>p2011</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>p00000_p2011</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4110</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Casale Di Scodosia-Marconi</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Piazza Matteotti 32/33, 35040 Casale Di Scodosia (PD)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>45.1883645404963</v>
-      </c>
-      <c r="J102" t="n">
         <v>11.4653727781197</v>
       </c>
     </row>

--- a/dati/CONSEGNE/CONSEGNE_26-03-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_26-03-2026/punti_consegna.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Punti consegna" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,8 +484,10 @@
           <t>p10839_p00000</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>3205</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -530,8 +532,10 @@
           <t>p11560_p00000</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>3110</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -576,8 +580,10 @@
           <t>p12264_p00000</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>3209</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -622,8 +628,10 @@
           <t>p12400_p00000</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>3206</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -668,8 +676,10 @@
           <t>p12472_p1855</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3206</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -714,8 +724,10 @@
           <t>p12528_p00000</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>3209</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -760,8 +772,10 @@
           <t>p13231_p00000</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3206</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -806,8 +820,10 @@
           <t>p13495_p00000</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>3206</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -852,8 +868,10 @@
           <t>p13590_p00000</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3206</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -898,8 +916,10 @@
           <t>p13927_p1853</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>3206</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -944,8 +964,10 @@
           <t>p13947_p00000</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>3205</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -990,8 +1012,10 @@
           <t>p14010_p00000</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>3110</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1036,8 +1060,10 @@
           <t>p14089_p2654</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>3209</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1082,8 +1108,10 @@
           <t>p2040_p00000</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>3111</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1128,8 +1156,10 @@
           <t>p2041_p00000</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>3111</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1174,8 +1204,10 @@
           <t>p2042_p00000</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>3111</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1220,8 +1252,10 @@
           <t>p2043_p00000</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>3111</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1266,8 +1300,10 @@
           <t>p2067_p00000</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>3110</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1312,8 +1348,10 @@
           <t>p2068_p00000</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>3110</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1358,8 +1396,10 @@
           <t>p2099_p00000</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>3206</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1404,8 +1444,10 @@
           <t>p2109_p1750</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>3110</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1450,8 +1492,10 @@
           <t>p2114_p1733</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>3209</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1496,8 +1540,10 @@
           <t>p2158_p00000</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>3110</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1542,8 +1588,10 @@
           <t>p2160_p00000</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>3110</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1588,8 +1636,10 @@
           <t>p2180_p1964</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>3209</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1634,8 +1684,10 @@
           <t>p2181_p1965</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>3209</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1680,8 +1732,10 @@
           <t>p2182_p1963</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>3209</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1726,8 +1780,10 @@
           <t>p2192_p2008</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>3111</v>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1772,8 +1828,10 @@
           <t>p2193_p2007</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>3111</v>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1818,8 +1876,10 @@
           <t>p2208_p00000</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>3111</v>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1864,8 +1924,10 @@
           <t>p2209_p1930</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>3111</v>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1910,8 +1972,10 @@
           <t>p2210_p00000</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>3111</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1956,8 +2020,10 @@
           <t>p2211_p00000</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>3111</v>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2002,8 +2068,10 @@
           <t>p2240_p1811</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>3111</v>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2048,8 +2116,10 @@
           <t>p2242_p1809</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>3111</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2094,8 +2164,10 @@
           <t>p2243_p1807</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>3111</v>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2140,8 +2212,10 @@
           <t>p2244_p1810</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>3111</v>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2186,8 +2260,10 @@
           <t>p2247_p1707</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>3111</v>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2232,8 +2308,10 @@
           <t>p2248_p1705</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>3111</v>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2278,8 +2356,10 @@
           <t>p2249_p1699</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>3111</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2324,8 +2404,10 @@
           <t>p2254_p1861</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>3206</v>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2370,8 +2452,10 @@
           <t>p2267_p1929</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>3206</v>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2416,8 +2500,10 @@
           <t>p2301_p1950</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>3205</v>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2462,8 +2548,10 @@
           <t>p2302_p1951</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>3205</v>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2508,8 +2596,10 @@
           <t>p2318_p2012</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>3209</v>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2554,8 +2644,10 @@
           <t>p2319_p2013</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>3209</v>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2600,8 +2692,10 @@
           <t>p2325_p1848</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>3110</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2646,8 +2740,10 @@
           <t>p2326_p1847</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>3110</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2692,8 +2788,10 @@
           <t>p2327_p1849</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>3110</v>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2738,8 +2836,10 @@
           <t>p2328_p1851</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>3110</v>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2784,8 +2884,10 @@
           <t>p2339_p00000</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>3209</v>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2830,8 +2932,10 @@
           <t>p2340_p1789</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>3209</v>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2876,8 +2980,10 @@
           <t>p2353_p00000</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>3206</v>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2922,8 +3028,10 @@
           <t>p2354_p1793</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>3206</v>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2968,8 +3076,10 @@
           <t>p2355_p1792</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>3205</v>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3014,8 +3124,10 @@
           <t>p2356_p1794</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>3205</v>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3060,8 +3172,10 @@
           <t>p2357_p1704</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>3205</v>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3106,8 +3220,10 @@
           <t>p2359_p1874</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>3209</v>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3152,8 +3268,10 @@
           <t>p2360_p1865</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>3209</v>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3198,8 +3316,10 @@
           <t>p2361_p1863</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>3209</v>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3244,8 +3364,10 @@
           <t>p2362_p1866</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>3209</v>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3290,8 +3412,10 @@
           <t>p2363_p1867</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>3209</v>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3336,8 +3460,10 @@
           <t>p2364_p1800</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>3110</v>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3382,8 +3508,10 @@
           <t>p2365_p00000</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>3110</v>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3428,8 +3556,10 @@
           <t>p2396_p00000</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>3206</v>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3474,8 +3604,10 @@
           <t>p2397_p00000</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>3206</v>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3520,8 +3652,10 @@
           <t>p2403_p00000</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>3111</v>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3566,8 +3700,10 @@
           <t>p2404_p00000</t>
         </is>
       </c>
-      <c r="D69" t="n">
-        <v>3111</v>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3612,8 +3748,10 @@
           <t>p2415_p2645</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>3111</v>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3658,8 +3796,10 @@
           <t>p2416_p2647</t>
         </is>
       </c>
-      <c r="D71" t="n">
-        <v>3111</v>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3704,8 +3844,10 @@
           <t>p2427_p00000</t>
         </is>
       </c>
-      <c r="D72" t="n">
-        <v>3110</v>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3750,8 +3892,10 @@
           <t>p2428_p00000</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>3110</v>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3796,8 +3940,10 @@
           <t>p2429_p1956</t>
         </is>
       </c>
-      <c r="D74" t="n">
-        <v>3110</v>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3842,8 +3988,10 @@
           <t>p2430_p1957</t>
         </is>
       </c>
-      <c r="D75" t="n">
-        <v>3110</v>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3888,8 +4036,10 @@
           <t>p6337_p1971</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>3110</v>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3934,8 +4084,10 @@
           <t>p6419_p1743</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>3110</v>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3980,8 +4132,10 @@
           <t>p6524_p00000</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>3206</v>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4026,8 +4180,10 @@
           <t>p6525_p00000</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>3206</v>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4072,8 +4228,10 @@
           <t>p6526_p00000</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>3206</v>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4118,8 +4276,10 @@
           <t>p6527_p00000</t>
         </is>
       </c>
-      <c r="D81" t="n">
-        <v>3205</v>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4164,8 +4324,10 @@
           <t>p6528_p00000</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>3206</v>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4210,8 +4372,10 @@
           <t>p7719_p00000</t>
         </is>
       </c>
-      <c r="D83" t="n">
-        <v>3205</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4256,8 +4420,10 @@
           <t>p8650_p1742</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>3110</v>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4302,8 +4468,10 @@
           <t>p8652_p1856</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>3206</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4348,8 +4516,10 @@
           <t>p8678_p1858</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>3206</v>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4394,8 +4564,10 @@
           <t>p8767_p00000</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>3205</v>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4440,8 +4612,10 @@
           <t>p8831_p00000</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>3205</v>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4486,8 +4660,10 @@
           <t>p8847_p00000</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>3206</v>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3206</t>
+        </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4532,8 +4708,10 @@
           <t>p8992_p2023</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>3110</v>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4578,8 +4756,10 @@
           <t>p9148_p00000</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>3209</v>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4624,8 +4804,10 @@
           <t>p00000_p1706</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>4111</v>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4670,8 +4852,10 @@
           <t>p00000_p1708</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>4111</v>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4716,8 +4900,10 @@
           <t>p00000_p1791</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>4119</v>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4762,8 +4948,10 @@
           <t>p00000_p1795</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>4119</v>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>4119</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4808,8 +4996,10 @@
           <t>p00000_p1797</t>
         </is>
       </c>
-      <c r="D96" t="n">
-        <v>4111</v>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4854,8 +5044,10 @@
           <t>p00000_p1819</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>4111</v>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4900,8 +5092,10 @@
           <t>p00000_p1901</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>4111</v>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4946,8 +5140,10 @@
           <t>p00000_p1911</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>4110</v>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4992,8 +5188,10 @@
           <t>p00000_p2011</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>4110</v>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>4110</t>
+        </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
